--- a/operations/vendor-source/vevor/2026-09-10/VEVOR_A_TIER_RUN_COMPLETE_2026-09-10_PUBLIC_SAFE.xlsx
+++ b/operations/vendor-source/vevor/2026-09-10/VEVOR_A_TIER_RUN_COMPLETE_2026-09-10_PUBLIC_SAFE.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>381</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -697,11 +697,11 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>89.90000000000001</v>
+        <v>80.91</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>89.90000000000001</v>
+        <v>80.91</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>168</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>164</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -841,11 +841,11 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>252.71</v>
+        <v>319.9</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>252.71</v>
+        <v>319.9</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>138</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -913,11 +913,11 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>184.94</v>
+        <v>166.45</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>184.94</v>
+        <v>166.45</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -985,11 +985,11 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>159.95</v>
+        <v>143.96</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>159.95</v>
+        <v>143.96</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>297</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Automotive &gt; Battery Charging Systems &gt; Car Battery Chargers &gt; RV Charger </t>
+          <t xml:space="preserve">Automotive &gt; Battery Charging Systems &gt; Car Battery Chargers &gt; Forklift and Scissor Lift Charger </t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1129,11 +1129,11 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>31.41</v>
+        <v>34.9</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>31.41</v>
+        <v>34.9</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>2576</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8570</t>
+          <t>8097</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1273,11 +1273,11 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>115.51</v>
+        <v>101.06</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>115.51</v>
+        <v>101.06</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>996</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1489,11 +1489,11 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>413.9</v>
+        <v>372.51</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>413.9</v>
+        <v>372.51</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>433</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>862</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1705,11 +1705,11 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>189.99</v>
+        <v>186.58</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
-        <v>189.99</v>
+        <v>186.58</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1777,11 +1777,11 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>66.90000000000001</v>
+        <v>60.21</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
-        <v>66.90000000000001</v>
+        <v>60.21</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>1473</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1849,11 +1849,11 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>59.9</v>
+        <v>53.91</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
-        <v>59.9</v>
+        <v>53.91</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2462</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>2860</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
